--- a/dataset/01.w_Defects/function_return_value_unchecked.xlsx
+++ b/dataset/01.w_Defects/function_return_value_unchecked.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>static int function_return_value_unchecked_010_var = MAX; extern volatile int vflag; void function_return_value_unchecked_001 () { int a; a = function_return_value_unchecked_001_func_002(1);/*Tool should detect this line as error*/ /*ERROR:Return value of function never checked*/ a++; } int function_return_value_unchecked_001_func_002(int flag) { int temp; temp = function_return_value_unchecked_001_func_001(flag); if (temp &gt; 0) { temp = temp+50; } else temp = 0; return temp; } else if (c &gt;0) { if ( function_return_value_unchecked_009_func_001( arr, (sizeof (arr)/sizeof (double)) ) == 0) c ++; } double function_return_value_unchecked_009_func_001(double a[] , int max ) { double ret =0.0; int i; for (i=0;i&lt;max;i++) ret += a[i]; return (ret); } int function_return_value_unchecked_001_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=flag++; return ret; }</t>
+          <t>static int function_return_value_unchecked_010_var = MAX; extern volatile int vflag; void function_return_value_unchecked_001 () { int a; a = function_return_value_unchecked_001_func_002(1);/*Tool should detect this line as error*/ /*ERROR:Return value of function never checked*/ a++; } int function_return_value_unchecked_001_func_002(int flag) { int temp; temp = function_return_value_unchecked_001_func_001(flag); if (temp &gt; 0) { temp = temp+50; } else temp = 0; return temp; } int function_return_value_unchecked_001_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=flag++; return ret; } else if (c &gt;0) { if ( function_return_value_unchecked_009_func_001( arr, (sizeof (arr)/sizeof (double)) ) == 0) c ++; } double function_return_value_unchecked_009_func_001(double a[] , int max ) { double ret =0.0; int i; for (i=0;i&lt;max;i++) ret += a[i]; return (ret); }</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>static int function_return_value_unchecked_010_var = MAX; extern volatile int vflag; void function_return_value_unchecked_003 () { int a=1; char buf = function_return_value_unchecked_003_func_001(); /*Tool should detect this line as error*/ /*ERROR:Return value of function never checked*/ a--; if (a!=0) { if(buf != '\0') printf("%c\n",buf); } } else if (c &gt;0) { if ( function_return_value_unchecked_009_func_001( arr, (sizeof (arr)/sizeof (double)) ) == 0) c ++; } double function_return_value_unchecked_009_func_001(double a[] , int max ) { double ret =0.0; int i; for (i=0;i&lt;max;i++) ret += a[i]; return (ret); } char function_return_value_unchecked_003_func_001(void) { char str1 = 'a'; return str1; }</t>
+          <t>static int function_return_value_unchecked_010_var = MAX; extern volatile int vflag; void function_return_value_unchecked_003 () { int a=1; char buf = function_return_value_unchecked_003_func_001(); /*Tool should detect this line as error*/ /*ERROR:Return value of function never checked*/ a--; if (a!=0) { if(buf != '\0') printf("%c\n",buf); } } char function_return_value_unchecked_003_func_001(void) { char str1 = 'a'; return str1; } else if (c &gt;0) { if ( function_return_value_unchecked_009_func_001( arr, (sizeof (arr)/sizeof (double)) ) == 0) c ++; } double function_return_value_unchecked_009_func_001(double a[] , int max ) { double ret =0.0; int i; for (i=0;i&lt;max;i++) ret += a[i]; return (ret); }</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>#define STR "string" typedef struct { float c; char *a; int b; } function_return_value_unchecked_005_s_001; static int function_return_value_unchecked_010_var = MAX; extern volatile int vflag; void function_return_value_unchecked_005 () { function_return_value_unchecked_005_s_001 u ; int i; for(i=0;i&lt;10;i++) { u = function_return_value_unchecked_005_s_001_func_001();/*Tool should detect this line as error*/ /*ERROR:Return value of function never checked*/ if (i==5) if(u.b &gt;0) u.c= 60.5; } } function_return_value_unchecked_005_s_001 function_return_value_unchecked_005_s_001_func_001 () { function_return_value_unchecked_005_s_001 u1; char *s ="This is STR"; u1.a = s; u1.b = 20; u1.c = 30.5; return u1; } else if (c &gt;0) { if ( function_return_value_unchecked_009_func_001( arr, (sizeof (arr)/sizeof (double)) ) == 0) c ++; } double function_return_value_unchecked_009_func_001(double a[] , int max ) { double ret =0.0; int i; for (i=0;i&lt;max;i++) ret += a[i]; return (ret); }</t>
+          <t>#define STR "string" typedef struct { float c; char *a; int b; } function_return_value_unchecked_005_s_001; static int function_return_value_unchecked_010_var = MAX; extern volatile int vflag; void function_return_value_unchecked_005 () { function_return_value_unchecked_005_s_001 u ; int i; for(i=0;i&lt;10;i++) { u = function_return_value_unchecked_005_s_001_func_001();/*Tool should detect this line as error*/ /*ERROR:Return value of function never checked*/ if (i==5) if(u.b &gt;0) u.c= 60.5; } } else if (c &gt;0) { if ( function_return_value_unchecked_009_func_001( arr, (sizeof (arr)/sizeof (double)) ) == 0) c ++; } double function_return_value_unchecked_009_func_001(double a[] , int max ) { double ret =0.0; int i; for (i=0;i&lt;max;i++) ret += a[i]; return (ret); } function_return_value_unchecked_005_s_001 function_return_value_unchecked_005_s_001_func_001 () { function_return_value_unchecked_005_s_001 u1; char *s ="This is STR"; u1.a = s; u1.b = 20; u1.c = 30.5; return u1; }</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
